--- a/output/palmer_drought_trendlines/state/Half-Decade.xlsx
+++ b/output/palmer_drought_trendlines/state/Half-Decade.xlsx
@@ -43,111 +43,111 @@
     <t>Trend Y</t>
   </si>
   <si>
+    <t>Arizona</t>
+  </si>
+  <si>
     <t>New Mexico</t>
   </si>
   <si>
     <t>Utah</t>
   </si>
   <si>
-    <t>Arizona</t>
-  </si>
-  <si>
     <t>Wyoming</t>
   </si>
   <si>
+    <t>California</t>
+  </si>
+  <si>
     <t>Nevada</t>
   </si>
   <si>
+    <t>Colorado</t>
+  </si>
+  <si>
     <t>Montana</t>
   </si>
   <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
     <t>Florida</t>
   </si>
   <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
     <t>Oregon</t>
   </si>
   <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
     <t>Idaho</t>
   </si>
   <si>
-    <t>Delaware</t>
-  </si>
-  <si>
-    <t>New Jersey</t>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Washington</t>
   </si>
   <si>
     <t>Connecticut</t>
   </si>
   <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
-    <t>Maryland</t>
-  </si>
-  <si>
-    <t>Washington</t>
-  </si>
-  <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>South Carolina</t>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
   </si>
   <si>
     <t>Nebraska</t>
   </si>
   <si>
-    <t>North Dakota</t>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
   </si>
   <si>
     <t>Kansas</t>
   </si>
   <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t>West Virginia</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Massachusetts</t>
-  </si>
-  <si>
-    <t>Pennsylvania</t>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
   </si>
   <si>
     <t>Missouri</t>
   </si>
   <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
     <t>Louisiana</t>
   </si>
   <si>
-    <t>Minnesota</t>
+    <t>Alabama</t>
   </si>
   <si>
     <t>Ohio</t>
   </si>
   <si>
-    <t>South Dakota</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
@@ -157,31 +157,31 @@
     <t>Mississippi</t>
   </si>
   <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
     <t>Illinois</t>
   </si>
   <si>
-    <t>Wisconsin</t>
-  </si>
-  <si>
-    <t>New Hampshire</t>
-  </si>
-  <si>
-    <t>Tennessee</t>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
   </si>
   <si>
     <t>Iowa</t>
   </si>
   <si>
-    <t>New York</t>
-  </si>
-  <si>
     <t>Indiana</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
   </si>
   <si>
     <t>Vermont</t>
@@ -576,89 +576,89 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.01969527223530691</v>
+        <v>-0.03499882781061292</v>
       </c>
       <c r="D2">
-        <v>1.095541851209963</v>
+        <v>1.639710892868606</v>
       </c>
       <c r="E2">
-        <v>-0.2949838358458228</v>
+        <v>-0.3085221005202278</v>
       </c>
       <c r="F2">
-        <v>0.0005956129740791239</v>
+        <v>0.0003192644600139826</v>
       </c>
       <c r="G2">
-        <v>0.005595305506838117</v>
+        <v>0.009464010784649772</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-1.464843539379935</v>
+        <v>-2.910136722511073</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.01916443923878933</v>
+        <v>-0.03433211374285898</v>
       </c>
       <c r="D3">
-        <v>1.161350210448131</v>
+        <v>1.882233134347519</v>
       </c>
       <c r="E3">
-        <v>-0.2835252469744542</v>
+        <v>-0.2935700915735422</v>
       </c>
       <c r="F3">
-        <v>0.0009865093057273683</v>
+        <v>0.0006345927987784405</v>
       </c>
       <c r="G3">
-        <v>0.005685063972870339</v>
+        <v>0.009804977017509073</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-1.330026890594482</v>
+        <v>-2.580941652224149</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.01849456136007263</v>
+        <v>-0.03338032361117284</v>
       </c>
       <c r="D4">
-        <v>0.8176622788919151</v>
+        <v>1.772580910199629</v>
       </c>
       <c r="E4">
-        <v>-0.300245920033311</v>
+        <v>-0.2752867800289296</v>
       </c>
       <c r="F4">
-        <v>0.0004690878236685714</v>
+        <v>0.001399848892925191</v>
       </c>
       <c r="G4">
-        <v>0.00515324409489229</v>
+        <v>0.01022399271237467</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-1.586630697917526</v>
+        <v>-2.566861159252841</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -669,141 +669,141 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.01839277810577639</v>
+        <v>-0.03264130708498127</v>
       </c>
       <c r="D5">
-        <v>1.222352933894529</v>
+        <v>1.778288080107838</v>
       </c>
       <c r="E5">
-        <v>-0.2442467714796441</v>
+        <v>-0.2610957335174589</v>
       </c>
       <c r="F5">
-        <v>0.004767031833089862</v>
+        <v>0.002495697795751544</v>
       </c>
       <c r="G5">
-        <v>0.006404571675407545</v>
+        <v>0.01058435030908872</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-1.168708219856401</v>
+        <v>-2.465081840939727</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.01716862696966684</v>
+        <v>-0.03196227465967501</v>
       </c>
       <c r="D6">
-        <v>0.7222502452935735</v>
+        <v>1.506416714808397</v>
       </c>
       <c r="E6">
-        <v>-0.2673056771647777</v>
+        <v>-0.3038468291458448</v>
       </c>
       <c r="F6">
-        <v>0.001945142593674795</v>
+        <v>0.0003973303908474349</v>
       </c>
       <c r="G6">
-        <v>0.005428224605395836</v>
+        <v>0.008789759349057884</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-1.509671260763116</v>
+        <v>-2.648678990949355</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.0171383548860152</v>
+        <v>-0.03150018713554242</v>
       </c>
       <c r="D7">
-        <v>1.299786154438668</v>
+        <v>1.335725271198408</v>
       </c>
       <c r="E7">
-        <v>-0.2778771197285206</v>
+        <v>-0.2612306643440849</v>
       </c>
       <c r="F7">
-        <v>0.001255429121221517</v>
+        <v>0.002482373143751129</v>
       </c>
       <c r="G7">
-        <v>0.005196306584580316</v>
+        <v>0.01020866596879904</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-0.9281999807433081</v>
+        <v>-2.759299056422107</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.01552315183372376</v>
+        <v>-0.02829490191431266</v>
       </c>
       <c r="D8">
-        <v>0.673904830678661</v>
+        <v>1.505955196097311</v>
       </c>
       <c r="E8">
-        <v>-0.2927782163212335</v>
+        <v>-0.2390240178689222</v>
       </c>
       <c r="F8">
-        <v>0.0006574379787861175</v>
+        <v>0.005776865813281152</v>
       </c>
       <c r="G8">
-        <v>0.00444640784815706</v>
+        <v>0.01008138758229188</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-1.344104907705428</v>
+        <v>-2.172382052763335</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.01550896021623925</v>
+        <v>-0.0274032222864112</v>
       </c>
       <c r="D9">
-        <v>0.9953310821343755</v>
+        <v>1.740146607612812</v>
       </c>
       <c r="E9">
-        <v>-0.2327149487164381</v>
+        <v>-0.2550501875497211</v>
       </c>
       <c r="F9">
-        <v>0.007247952643976476</v>
+        <v>0.003163312831107595</v>
       </c>
       <c r="G9">
-        <v>0.005684554361375047</v>
+        <v>0.009111678011718281</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-1.020833745976727</v>
+        <v>-1.822272289620643</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -814,83 +814,83 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.01146497489929033</v>
+        <v>-0.02290440089469552</v>
       </c>
       <c r="D10">
-        <v>0.5382395761693858</v>
+        <v>1.077096476025419</v>
       </c>
       <c r="E10">
-        <v>-0.2683496310549199</v>
+        <v>-0.229136272620056</v>
       </c>
       <c r="F10">
-        <v>0.001864253805507255</v>
+        <v>0.00822249347519111</v>
       </c>
       <c r="G10">
-        <v>0.003609705082902366</v>
+        <v>0.008533795652280128</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-0.9522071607383568</v>
+        <v>-1.900475640284999</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.007796788999561964</v>
+        <v>-0.02087542105497045</v>
       </c>
       <c r="D11">
-        <v>0.2279644989133725</v>
+        <v>1.019826304640863</v>
       </c>
       <c r="E11">
-        <v>-0.1829754848013755</v>
+        <v>-0.219085557318187</v>
       </c>
       <c r="F11">
-        <v>0.03572914169029178</v>
+        <v>0.01160604722631047</v>
       </c>
       <c r="G11">
-        <v>0.003674147734419536</v>
+        <v>0.008153961182599085</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-0.785618071029683</v>
+        <v>-1.693978432505296</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.007195535551168136</v>
+        <v>-0.01793176218479512</v>
       </c>
       <c r="D12">
-        <v>0.2191976470156715</v>
+        <v>0.6255138327235382</v>
       </c>
       <c r="E12">
-        <v>-0.1487942121364976</v>
+        <v>-0.1849051748312367</v>
       </c>
       <c r="F12">
-        <v>0.08861524577162064</v>
+        <v>0.03379314189986493</v>
       </c>
       <c r="G12">
-        <v>0.004194148588107898</v>
+        <v>0.008358880080670095</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-0.7162219746361862</v>
+        <v>-1.705615251299827</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -901,286 +901,286 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.004457694106394281</v>
+        <v>-0.01777432737363413</v>
       </c>
       <c r="D13">
-        <v>0.0519067701026108</v>
+        <v>0.7030889017266835</v>
       </c>
       <c r="E13">
-        <v>-0.1114265404808094</v>
+        <v>-0.1862612705931858</v>
       </c>
       <c r="F13">
-        <v>0.2033793904747122</v>
+        <v>0.03248630086234521</v>
       </c>
       <c r="G13">
-        <v>0.003486879911344075</v>
+        <v>0.008223024923958308</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-0.5275934637286458</v>
+        <v>-1.607573656845754</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.004011563960784064</v>
+        <v>-0.01735977721488988</v>
       </c>
       <c r="D14">
-        <v>0.2348678715853759</v>
+        <v>0.6849878682842294</v>
       </c>
       <c r="E14">
-        <v>-0.1096343074748629</v>
+        <v>-0.1831781810905936</v>
       </c>
       <c r="F14">
-        <v>0.210789335727573</v>
+        <v>0.03552148348829411</v>
       </c>
       <c r="G14">
-        <v>0.003189845979461038</v>
+        <v>0.008171230661419024</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>-0.2866354433165524</v>
+        <v>-1.571783169651455</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.003868516508204551</v>
+        <v>-0.01690683217546303</v>
       </c>
       <c r="D15">
-        <v>0.1414593179463198</v>
+        <v>0.8343468772064961</v>
       </c>
       <c r="E15">
-        <v>-0.1057365472932424</v>
+        <v>-0.1809355391078904</v>
       </c>
       <c r="F15">
-        <v>0.2275662499196597</v>
+        <v>0.03787659436807654</v>
       </c>
       <c r="G15">
-        <v>0.003190848808897228</v>
+        <v>0.008060070196882258</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-0.3614478281202719</v>
+        <v>-1.363541305603697</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.003250600942801984</v>
+        <v>-0.01685350595229278</v>
       </c>
       <c r="D16">
-        <v>0.09269194336698677</v>
+        <v>0.5685352076513256</v>
       </c>
       <c r="E16">
-        <v>-0.08588138262065767</v>
+        <v>-0.1692935190392257</v>
       </c>
       <c r="F16">
-        <v>0.327516909722627</v>
+        <v>0.05231093448808986</v>
       </c>
       <c r="G16">
-        <v>0.003307390113600722</v>
+        <v>0.008605256512380833</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>-0.3298861791972711</v>
+        <v>-1.622420566146736</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.003103409915714943</v>
+        <v>-0.01556547423306522</v>
       </c>
       <c r="D17">
-        <v>0.01482014249951863</v>
+        <v>0.6002765260928173</v>
       </c>
       <c r="E17">
-        <v>-0.07927289868818932</v>
+        <v>-0.1634458304014108</v>
       </c>
       <c r="F17">
-        <v>0.3662411466936193</v>
+        <v>0.06112332642005634</v>
       </c>
       <c r="G17">
-        <v>0.003422739348348117</v>
+        <v>0.008240184819246278</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>-0.3886231465434239</v>
+        <v>-1.423235124205661</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.00307832712252123</v>
+        <v>-0.01518565722101251</v>
       </c>
       <c r="D18">
-        <v>0.02443172127314244</v>
+        <v>0.5159474934206303</v>
       </c>
       <c r="E18">
-        <v>-0.08016388690651854</v>
+        <v>-0.1570992687524294</v>
       </c>
       <c r="F18">
-        <v>0.360861575690426</v>
+        <v>0.07202599615360503</v>
       </c>
       <c r="G18">
-        <v>0.003357100794228077</v>
+        <v>0.008372618013094489</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-0.3757508046546175</v>
+        <v>-1.458187945310996</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.003010839965605999</v>
+        <v>-0.01493699704236966</v>
       </c>
       <c r="D19">
-        <v>-0.1053512787360273</v>
+        <v>0.5485610116182038</v>
       </c>
       <c r="E19">
-        <v>-0.04567363615730881</v>
+        <v>-0.1608003661844165</v>
       </c>
       <c r="F19">
-        <v>0.6030422245279292</v>
+        <v>0.06549138964558252</v>
       </c>
       <c r="G19">
-        <v>0.005775597878876706</v>
+        <v>0.008041109876186222</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-0.4967604742648071</v>
+        <v>-1.393248603889851</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.002864993027384708</v>
+        <v>-0.0146095226809265</v>
       </c>
       <c r="D20">
-        <v>0.04209408269373602</v>
+        <v>0.5693246036330961</v>
       </c>
       <c r="E20">
-        <v>-0.06356245697850822</v>
+        <v>-0.1602598578563123</v>
       </c>
       <c r="F20">
-        <v>0.469026542373564</v>
+        <v>0.06641442614929018</v>
       </c>
       <c r="G20">
-        <v>0.003945228162349976</v>
+        <v>0.007892047459744034</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>-0.3303550108662761</v>
+        <v>-1.329913344887349</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.002524632553402051</v>
+        <v>-0.01377495543804036</v>
       </c>
       <c r="D21">
-        <v>0.003659784691847107</v>
+        <v>0.3355025354644074</v>
       </c>
       <c r="E21">
-        <v>-0.06125141653717175</v>
+        <v>-0.115908745682982</v>
       </c>
       <c r="F21">
-        <v>0.485372709525363</v>
+        <v>0.1856725907150618</v>
       </c>
       <c r="G21">
-        <v>0.003608229505940475</v>
+        <v>0.0103529760224964</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-0.3245424472504196</v>
+        <v>-1.45524167148084</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-0.0002468664848214268</v>
+        <v>-0.01331415564344507</v>
       </c>
       <c r="D22">
-        <v>0.6163535299349858</v>
+        <v>0.653882790936517</v>
       </c>
       <c r="E22">
-        <v>-0.003440752538485355</v>
+        <v>-0.1418266652783684</v>
       </c>
       <c r="F22">
-        <v>0.9687665234079531</v>
+        <v>0.1047654233716014</v>
       </c>
       <c r="G22">
-        <v>0.006292662612071857</v>
+        <v>0.008150263696321543</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>0.5842608869082003</v>
+        <v>-1.076957442711342</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1191,402 +1191,402 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>0.0009057000512806448</v>
+        <v>-0.01207330973154197</v>
       </c>
       <c r="D23">
-        <v>0.6492116906458325</v>
+        <v>1.271272995699339</v>
       </c>
       <c r="E23">
-        <v>0.01479975677600001</v>
+        <v>-0.1075284150815871</v>
       </c>
       <c r="F23">
-        <v>0.8662464025969703</v>
+        <v>0.2197403465638854</v>
       </c>
       <c r="G23">
-        <v>0.00536674018231303</v>
+        <v>0.00979052676708048</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>0.7669526973123163</v>
+        <v>-0.298257269401117</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24">
-        <v>0.001829960872941809</v>
+        <v>-0.01055034834861525</v>
       </c>
       <c r="D24">
-        <v>0.1737288382712993</v>
+        <v>1.055388920983375</v>
       </c>
       <c r="E24">
-        <v>0.02926205164589126</v>
+        <v>-0.0891229441486002</v>
       </c>
       <c r="F24">
-        <v>0.7390821277877333</v>
+        <v>0.30952006264001</v>
       </c>
       <c r="G24">
-        <v>0.005482508826967556</v>
+        <v>0.0103412713340683</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>0.4116237517537344</v>
+        <v>-0.316156364336607</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25">
-        <v>0.001861638765624902</v>
+        <v>-0.009195230265594217</v>
       </c>
       <c r="D25">
-        <v>-0.1225853759181316</v>
+        <v>0.2679949932601579</v>
       </c>
       <c r="E25">
-        <v>0.04787733971220831</v>
+        <v>-0.100870916509646</v>
       </c>
       <c r="F25">
-        <v>0.5856505531436444</v>
+        <v>0.2498005969296761</v>
       </c>
       <c r="G25">
-        <v>0.003406398099899948</v>
+        <v>0.007954340692546061</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>0.1194276636131056</v>
+        <v>-0.9273849412670904</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26">
-        <v>0.002093596550442306</v>
+        <v>-0.008815640383751301</v>
       </c>
       <c r="D26">
-        <v>0.05968941248750595</v>
+        <v>0.3709783683163232</v>
       </c>
       <c r="E26">
-        <v>0.05143823273734497</v>
+        <v>-0.09879207130907347</v>
       </c>
       <c r="F26">
-        <v>0.5580453224509512</v>
+        <v>0.259743180540187</v>
       </c>
       <c r="G26">
-        <v>0.003565003571228044</v>
+        <v>0.007788079191376402</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>0.3318569640450056</v>
+        <v>-0.7750548815713458</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27">
-        <v>0.002987863276078181</v>
+        <v>-0.008758887456981043</v>
       </c>
       <c r="D27">
-        <v>-0.08875736109964887</v>
+        <v>0.5608833686372681</v>
       </c>
       <c r="E27">
-        <v>0.09092920200044452</v>
+        <v>-0.09445622429520335</v>
       </c>
       <c r="F27">
-        <v>0.2997775723014957</v>
+        <v>0.2813425372378646</v>
       </c>
       <c r="G27">
-        <v>0.002870005980171094</v>
+        <v>0.00809656135172593</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>0.2996648647905146</v>
+        <v>-0.5777720007702676</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
       <c r="C28">
-        <v>0.003966019204494077</v>
+        <v>-0.007929662711638448</v>
       </c>
       <c r="D28">
-        <v>-0.2999283880315078</v>
+        <v>0.3306077411900635</v>
       </c>
       <c r="E28">
-        <v>0.1110091911413263</v>
+        <v>-0.08530625301543525</v>
       </c>
       <c r="F28">
-        <v>0.2050879359177948</v>
+        <v>0.330778723766171</v>
       </c>
       <c r="G28">
-        <v>0.003114093584452746</v>
+        <v>0.00812299489071293</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>0.2156541085527222</v>
+        <v>-0.7002484113229347</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29">
-        <v>0.005226425823999484</v>
+        <v>-0.007638837290830353</v>
       </c>
       <c r="D29">
-        <v>-0.2412212089534448</v>
+        <v>0.5988508890172665</v>
       </c>
       <c r="E29">
-        <v>0.1208648541332453</v>
+        <v>-0.07088682306503555</v>
       </c>
       <c r="F29">
-        <v>0.1674357139637407</v>
+        <v>0.4192643674027062</v>
       </c>
       <c r="G29">
-        <v>0.003764762030088031</v>
+        <v>0.009427491889430982</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>0.4382141481664881</v>
+        <v>-0.3941979587906794</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30">
-        <v>0.005540328943795152</v>
+        <v>-0.007396692786640792</v>
       </c>
       <c r="D30">
-        <v>0.04161117530008318</v>
+        <v>0.3089742602220937</v>
       </c>
       <c r="E30">
-        <v>0.1097432658788199</v>
+        <v>-0.07625247221676541</v>
       </c>
       <c r="F30">
-        <v>0.2103334122835362</v>
+        <v>0.384842871292438</v>
       </c>
       <c r="G30">
-        <v>0.00440103565586439</v>
+        <v>0.008482926456500239</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>0.7618539379934529</v>
+        <v>-0.6525958020412093</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>38</v>
       </c>
       <c r="C31">
-        <v>0.00560580917253361</v>
+        <v>-0.00665261224429335</v>
       </c>
       <c r="D31">
-        <v>-0.3955768066903249</v>
+        <v>0.5095112651646446</v>
       </c>
       <c r="E31">
-        <v>0.128487462502095</v>
+        <v>-0.06617296879275812</v>
       </c>
       <c r="F31">
-        <v>0.1420332914999296</v>
+        <v>0.4509301359504699</v>
       </c>
       <c r="G31">
-        <v>0.003794819033559501</v>
+        <v>0.008798061017374131</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>0.3331783857390444</v>
+        <v>-0.3553283265934909</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
         <v>39</v>
       </c>
       <c r="C32">
-        <v>0.005762503412243446</v>
+        <v>-0.006159698213077757</v>
       </c>
       <c r="D32">
-        <v>-0.5963051635443316</v>
+        <v>1.323932344823159</v>
       </c>
       <c r="E32">
-        <v>0.1325243525334448</v>
+        <v>-0.05120454261350543</v>
       </c>
       <c r="F32">
-        <v>0.1298238695061585</v>
+        <v>0.5598376271021979</v>
       </c>
       <c r="G32">
-        <v>0.003780038723540898</v>
+        <v>0.01053681076634849</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>0.1528202800473164</v>
+        <v>0.5231715771230506</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
         <v>40</v>
       </c>
       <c r="C33">
-        <v>0.005968361890372291</v>
+        <v>-0.005799365022935216</v>
       </c>
       <c r="D33">
-        <v>0.007101730351296964</v>
+        <v>0.5680884524038772</v>
       </c>
       <c r="E33">
-        <v>0.1074661976927701</v>
+        <v>-0.05875176854337051</v>
       </c>
       <c r="F33">
-        <v>0.2200088377620975</v>
+        <v>0.5033904440216205</v>
       </c>
       <c r="G33">
-        <v>0.004842717836898426</v>
+        <v>0.008642452185960558</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>0.7829887760996947</v>
+        <v>-0.1858290005777009</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
       </c>
       <c r="C34">
-        <v>0.006843777443430825</v>
+        <v>-0.005083093118448402</v>
       </c>
       <c r="D34">
-        <v>-0.220150270969162</v>
+        <v>-0.1084969510238142</v>
       </c>
       <c r="E34">
-        <v>0.1555042398317233</v>
+        <v>-0.05263004568515698</v>
       </c>
       <c r="F34">
-        <v>0.07500034089714015</v>
+        <v>0.5489477725638865</v>
       </c>
       <c r="G34">
-        <v>0.003812997106692189</v>
+        <v>0.008459025363370804</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>0.6695407966768453</v>
+        <v>-0.7692990564221065</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="B35" t="s">
         <v>42</v>
       </c>
       <c r="C35">
-        <v>0.006959176730580545</v>
+        <v>-0.004579008231001298</v>
       </c>
       <c r="D35">
-        <v>0.625021957213465</v>
+        <v>-0.1267046665382888</v>
       </c>
       <c r="E35">
-        <v>0.09475521271214234</v>
+        <v>-0.04883364688320311</v>
       </c>
       <c r="F35">
-        <v>0.2798155324961381</v>
+        <v>0.5781756602491933</v>
       </c>
       <c r="G35">
-        <v>0.006412459067086948</v>
+        <v>0.008214140644072837</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>1.529714932188936</v>
+        <v>-0.7219757365684576</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
       </c>
       <c r="C36">
-        <v>0.00739303041781378</v>
+        <v>-0.004452453253146496</v>
       </c>
       <c r="D36">
-        <v>-0.6616934563927632</v>
+        <v>0.1775036908659094</v>
       </c>
       <c r="E36">
-        <v>0.1796095230928559</v>
+        <v>-0.0481267291728188</v>
       </c>
       <c r="F36">
-        <v>0.0393298880468456</v>
+        <v>0.5836969519920225</v>
       </c>
       <c r="G36">
-        <v>0.00355141068831985</v>
+        <v>0.008104716156317976</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>0.2994004979230283</v>
+        <v>-0.4013152320431351</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1597,25 +1597,25 @@
         <v>44</v>
       </c>
       <c r="C37">
-        <v>0.008107271340893528</v>
+        <v>-0.004417601603736785</v>
       </c>
       <c r="D37">
-        <v>-0.5323390599066511</v>
+        <v>0.07059284934848184</v>
       </c>
       <c r="E37">
-        <v>0.1962737785829258</v>
+        <v>-0.04798120259315904</v>
       </c>
       <c r="F37">
-        <v>0.02409868814220353</v>
+        <v>0.5848365750456381</v>
       </c>
       <c r="G37">
-        <v>0.003552303873563123</v>
+        <v>0.008065722018170688</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>0.5216062144095075</v>
+        <v>-0.5036953591373001</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1626,25 +1626,25 @@
         <v>45</v>
       </c>
       <c r="C38">
-        <v>0.008357587806634601</v>
+        <v>-0.002715821594157815</v>
       </c>
       <c r="D38">
-        <v>-0.3900210493979993</v>
+        <v>0.1099911419218178</v>
       </c>
       <c r="E38">
-        <v>0.1568306340781449</v>
+        <v>-0.02597416066302262</v>
       </c>
       <c r="F38">
-        <v>0.07252013880266329</v>
+        <v>0.7675111841543407</v>
       </c>
       <c r="G38">
-        <v>0.004616051798794405</v>
+        <v>0.009167300955513996</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>0.6964653654644989</v>
+        <v>-0.2430656653186982</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1655,286 +1655,286 @@
         <v>46</v>
       </c>
       <c r="C39">
-        <v>0.00897694233361478</v>
+        <v>-0.002536045070533803</v>
       </c>
       <c r="D39">
-        <v>-0.699204506065858</v>
+        <v>-0.1488024905321267</v>
       </c>
       <c r="E39">
-        <v>0.2054389597709201</v>
+        <v>-0.02671768801103801</v>
       </c>
       <c r="F39">
-        <v>0.01812137484402738</v>
+        <v>0.76105355612361</v>
       </c>
       <c r="G39">
-        <v>0.003750681591493521</v>
+        <v>0.008322069810507675</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>0.4677979973040634</v>
+        <v>-0.4784883497015212</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
       </c>
       <c r="C40">
-        <v>0.01044766405043702</v>
+        <v>-0.001349032968443713</v>
       </c>
       <c r="D40">
-        <v>-0.477419525368399</v>
+        <v>0.08632556646768084</v>
       </c>
       <c r="E40">
-        <v>0.2162951045019205</v>
+        <v>-0.01403696615372829</v>
       </c>
       <c r="F40">
-        <v>0.01273961249592403</v>
+        <v>0.8730808239305847</v>
       </c>
       <c r="G40">
-        <v>0.004136152970919209</v>
+        <v>0.008428200223546163</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>0.8807768011884132</v>
+        <v>-0.08904871943000191</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
         <v>48</v>
       </c>
       <c r="C41">
-        <v>0.0106829285548523</v>
+        <v>-0.0001303905158324539</v>
       </c>
       <c r="D41">
-        <v>-0.3227222130523693</v>
+        <v>-0.2298738044803905</v>
       </c>
       <c r="E41">
-        <v>0.2270098427207611</v>
+        <v>-0.001422587007171103</v>
       </c>
       <c r="F41">
-        <v>0.008854932628825538</v>
+        <v>0.9870837437549744</v>
       </c>
       <c r="G41">
-        <v>0.004019619692643888</v>
+        <v>0.008038870821792242</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>1.06605849907843</v>
+        <v>-0.2468245715386095</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.01139075749335715</v>
+        <v>0.0002518064258098944</v>
       </c>
       <c r="D42">
-        <v>-0.7641600047683238</v>
+        <v>-0.04705603697284817</v>
       </c>
       <c r="E42">
-        <v>0.2828387572496878</v>
+        <v>0.002818326509322505</v>
       </c>
       <c r="F42">
-        <v>0.001016112647305845</v>
+        <v>0.9744144779089743</v>
       </c>
       <c r="G42">
-        <v>0.003387945778689751</v>
+        <v>0.00783613847579742</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>0.7166384693681055</v>
+        <v>-0.0143212016175619</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.01173983412440952</v>
+        <v>0.0003062920005727667</v>
       </c>
       <c r="D43">
-        <v>-0.6586963173869589</v>
+        <v>0.1223869311252325</v>
       </c>
       <c r="E43">
-        <v>0.2479745680678548</v>
+        <v>0.003327389223261482</v>
       </c>
       <c r="F43">
-        <v>0.004146045078760055</v>
+        <v>0.9697950860959663</v>
       </c>
       <c r="G43">
-        <v>0.004022557617907836</v>
+        <v>0.00807342785046994</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>0.8674821187862785</v>
+        <v>0.1622048911996921</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.01212986021616871</v>
+        <v>0.0008897263080971964</v>
       </c>
       <c r="D44">
-        <v>-0.3270243276205152</v>
+        <v>-0.1724774375762246</v>
       </c>
       <c r="E44">
-        <v>0.2244804683760959</v>
+        <v>0.009163589035299102</v>
       </c>
       <c r="F44">
-        <v>0.009662842984708613</v>
+        <v>0.9169452040855257</v>
       </c>
       <c r="G44">
-        <v>0.004618254490820871</v>
+        <v>0.008515318906570682</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>1.249857500481418</v>
+        <v>-0.05681301752358908</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.01262630929632663</v>
+        <v>0.002791432253477318</v>
       </c>
       <c r="D45">
-        <v>-0.6385420896261453</v>
+        <v>-0.375728480647025</v>
       </c>
       <c r="E45">
-        <v>0.3195369322395472</v>
+        <v>0.03214974949423369</v>
       </c>
       <c r="F45">
-        <v>0.0001879525792544095</v>
+        <v>0.7143994382031913</v>
       </c>
       <c r="G45">
-        <v>0.003283951546153708</v>
+        <v>0.007611202240236833</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>1.002878118896317</v>
+        <v>-0.0128422876949737</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.01321392456314467</v>
+        <v>0.00305389799878535</v>
       </c>
       <c r="D46">
-        <v>-0.6474842737017781</v>
+        <v>-0.3110121317157714</v>
       </c>
       <c r="E46">
-        <v>0.2995053130771425</v>
+        <v>0.03222282929323416</v>
       </c>
       <c r="F46">
-        <v>0.0004852540391272627</v>
+        <v>0.7137784766665933</v>
       </c>
       <c r="G46">
-        <v>0.003691875683167026</v>
+        <v>0.00830794470284801</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>1.070325919507029</v>
+        <v>0.0859946081263242</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.01343443900601612</v>
+        <v>0.003254841082917338</v>
       </c>
       <c r="D47">
-        <v>-0.797226981376028</v>
+        <v>0.01624866807882425</v>
       </c>
       <c r="E47">
-        <v>0.329112430265588</v>
+        <v>0.0327184088457845</v>
       </c>
       <c r="F47">
-        <v>0.0001166032000526097</v>
+        <v>0.7095724817789599</v>
       </c>
       <c r="G47">
-        <v>0.003380720808816498</v>
+        <v>0.008720338803628595</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>0.9492500894060683</v>
+        <v>0.4393780088580782</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.01414876408013323</v>
+        <v>0.005011335772514281</v>
       </c>
       <c r="D48">
-        <v>-0.8056187312591128</v>
+        <v>-0.4462377559535272</v>
       </c>
       <c r="E48">
-        <v>0.2935963782166084</v>
+        <v>0.05512020452580395</v>
       </c>
       <c r="F48">
-        <v>0.000633847113144166</v>
+        <v>0.5301761491418182</v>
       </c>
       <c r="G48">
-        <v>0.004040377921117827</v>
+        <v>0.007961781540550989</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>1.033720599158207</v>
+        <v>0.2052358944733293</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1945,25 +1945,25 @@
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.01653134439217629</v>
+        <v>0.005204532728969473</v>
       </c>
       <c r="D49">
-        <v>-1.14441712745179</v>
+        <v>-0.6010606585788563</v>
       </c>
       <c r="E49">
-        <v>0.4081522845274992</v>
+        <v>0.0568700823165629</v>
       </c>
       <c r="F49">
-        <v>1.185862213838862E-06</v>
+        <v>0.5171806323870285</v>
       </c>
       <c r="G49">
-        <v>0.003242978470481063</v>
+        <v>0.008013509826736464</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>1.004657643531127</v>
+        <v>0.07552859618717522</v>
       </c>
     </row>
   </sheetData>

--- a/output/palmer_drought_trendlines/state/Half-Decade.xlsx
+++ b/output/palmer_drought_trendlines/state/Half-Decade.xlsx
@@ -55,12 +55,12 @@
     <t>Wyoming</t>
   </si>
   <si>
+    <t>Nevada</t>
+  </si>
+  <si>
     <t>California</t>
   </si>
   <si>
-    <t>Nevada</t>
-  </si>
-  <si>
     <t>Colorado</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Massachusetts</t>
   </si>
   <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>West Virginia</t>
-  </si>
-  <si>
     <t>Pennsylvania</t>
   </si>
   <si>
@@ -145,12 +145,12 @@
     <t>Alabama</t>
   </si>
   <si>
+    <t>Maine</t>
+  </si>
+  <si>
     <t>Ohio</t>
   </si>
   <si>
-    <t>Maine</t>
-  </si>
-  <si>
     <t>Oklahoma</t>
   </si>
   <si>
@@ -172,19 +172,19 @@
     <t>Illinois</t>
   </si>
   <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
     <t>Michigan</t>
   </si>
   <si>
-    <t>Kentucky</t>
-  </si>
-  <si>
     <t>Iowa</t>
   </si>
   <si>
+    <t>Vermont</t>
+  </si>
+  <si>
     <t>Indiana</t>
-  </si>
-  <si>
-    <t>Vermont</t>
   </si>
 </sst>
 </file>
@@ -582,25 +582,25 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.03499882781061292</v>
+        <v>-0.02419524606595664</v>
       </c>
       <c r="D2">
-        <v>1.639710892868606</v>
+        <v>1.189561653507928</v>
       </c>
       <c r="E2">
-        <v>-0.3085221005202278</v>
+        <v>-0.3164246030049608</v>
       </c>
       <c r="F2">
-        <v>0.0003192644600139826</v>
+        <v>0.0002187599952524957</v>
       </c>
       <c r="G2">
-        <v>0.009464010784649772</v>
+        <v>0.006361790013420917</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-2.910136722511073</v>
+        <v>-1.955820335066436</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -611,25 +611,25 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.03433211374285898</v>
+        <v>-0.02351524488092946</v>
       </c>
       <c r="D3">
-        <v>1.882233134347519</v>
+        <v>1.431530265100456</v>
       </c>
       <c r="E3">
-        <v>-0.2935700915735422</v>
+        <v>-0.289793116474233</v>
       </c>
       <c r="F3">
-        <v>0.0006345927987784405</v>
+        <v>0.0007505194584138874</v>
       </c>
       <c r="G3">
-        <v>0.009804977017509073</v>
+        <v>0.006811491676588512</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-2.580941652224149</v>
+        <v>-1.625451569420374</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -640,25 +640,25 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.03338032361117284</v>
+        <v>-0.02280146745865984</v>
       </c>
       <c r="D4">
-        <v>1.772580910199629</v>
+        <v>1.331795237178253</v>
       </c>
       <c r="E4">
-        <v>-0.2752867800289296</v>
+        <v>-0.2680255125170195</v>
       </c>
       <c r="F4">
-        <v>0.001399848892925191</v>
+        <v>0.001889034429598372</v>
       </c>
       <c r="G4">
-        <v>0.01022399271237467</v>
+        <v>0.007188312596064567</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-2.566861159252841</v>
+        <v>-1.632395532447526</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -669,83 +669,83 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.03264130708498127</v>
+        <v>-0.02194864388451911</v>
       </c>
       <c r="D5">
-        <v>1.778288080107838</v>
+        <v>1.332760446755248</v>
       </c>
       <c r="E5">
-        <v>-0.2610957335174589</v>
+        <v>-0.2404884460230541</v>
       </c>
       <c r="F5">
-        <v>0.002495697795751544</v>
+        <v>0.005476059692904376</v>
       </c>
       <c r="G5">
-        <v>0.01058435030908872</v>
+        <v>0.007769719748119197</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-2.465081840939727</v>
+        <v>-1.520563258232236</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.03196227465967501</v>
+        <v>-0.02085431769591216</v>
       </c>
       <c r="D6">
-        <v>1.506416714808397</v>
+        <v>0.8921473778804809</v>
       </c>
       <c r="E6">
-        <v>-0.3038468291458448</v>
+        <v>-0.2443577566100546</v>
       </c>
       <c r="F6">
-        <v>0.0003973303908474349</v>
+        <v>0.004747403728279791</v>
       </c>
       <c r="G6">
-        <v>0.008789759349057884</v>
+        <v>0.007258199879796701</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-2.648678990949355</v>
+        <v>-1.8189139225881</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.03150018713554242</v>
+        <v>-0.02078607593061666</v>
       </c>
       <c r="D7">
-        <v>1.335725271198408</v>
+        <v>1.040741767764298</v>
       </c>
       <c r="E7">
-        <v>-0.2612306643440849</v>
+        <v>-0.303728055931229</v>
       </c>
       <c r="F7">
-        <v>0.002482373143751129</v>
+        <v>0.0003995257665417422</v>
       </c>
       <c r="G7">
-        <v>0.01020866596879904</v>
+        <v>0.005718720572117681</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-2.759299056422107</v>
+        <v>-1.661448103215867</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -756,25 +756,25 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.02829490191431266</v>
+        <v>-0.01780443397670434</v>
       </c>
       <c r="D8">
-        <v>1.505955196097311</v>
+        <v>1.068852365363631</v>
       </c>
       <c r="E8">
-        <v>-0.2390240178689222</v>
+        <v>-0.2227147969121397</v>
       </c>
       <c r="F8">
-        <v>0.005776865813281152</v>
+        <v>0.01026465370344833</v>
       </c>
       <c r="G8">
-        <v>0.01008138758229188</v>
+        <v>0.006835341346486132</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-2.172382052763335</v>
+        <v>-1.245724051607934</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -785,25 +785,25 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.0274032222864112</v>
+        <v>-0.01598554464343026</v>
       </c>
       <c r="D9">
-        <v>1.740146607612812</v>
+        <v>1.264410039155274</v>
       </c>
       <c r="E9">
-        <v>-0.2550501875497211</v>
+        <v>-0.2166991307059231</v>
       </c>
       <c r="F9">
-        <v>0.003163312831107595</v>
+        <v>0.01256971152724577</v>
       </c>
       <c r="G9">
-        <v>0.009111678011718281</v>
+        <v>0.006316179962349502</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-1.822272289620643</v>
+        <v>-0.8137107644906609</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -814,25 +814,25 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.02290440089469552</v>
+        <v>-0.01203553896517501</v>
       </c>
       <c r="D10">
-        <v>1.077096476025419</v>
+        <v>0.6242272289620643</v>
       </c>
       <c r="E10">
-        <v>-0.229136272620056</v>
+        <v>-0.2192224808719221</v>
       </c>
       <c r="F10">
-        <v>0.00822249347519111</v>
+        <v>0.0115527765726226</v>
       </c>
       <c r="G10">
-        <v>0.008533795652280128</v>
+        <v>0.004698009708748499</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-1.900475640284999</v>
+        <v>-0.9403928365106875</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -843,25 +843,25 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.02087542105497045</v>
+        <v>-0.009824583388881484</v>
       </c>
       <c r="D11">
-        <v>1.019826304640863</v>
+        <v>0.5593747352204893</v>
       </c>
       <c r="E11">
-        <v>-0.219085557318187</v>
+        <v>-0.2006963711389975</v>
       </c>
       <c r="F11">
-        <v>0.01160604722631047</v>
+        <v>0.02103120912673909</v>
       </c>
       <c r="G11">
-        <v>0.008153961182599085</v>
+        <v>0.004206059756204978</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-1.693978432505296</v>
+        <v>-0.7178211053341036</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -872,25 +872,25 @@
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.01793176218479512</v>
+        <v>-0.006880924518706149</v>
       </c>
       <c r="D12">
-        <v>0.6255138327235382</v>
+        <v>0.1650622633031646</v>
       </c>
       <c r="E12">
-        <v>-0.1849051748312367</v>
+        <v>-0.1302483503917707</v>
       </c>
       <c r="F12">
-        <v>0.03379314189986493</v>
+        <v>0.1366044901591242</v>
       </c>
       <c r="G12">
-        <v>0.008358880080670095</v>
+        <v>0.004593962624278612</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-1.705615251299827</v>
+        <v>-0.7294579241286347</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -901,25 +901,25 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.01777432737363413</v>
+        <v>-0.006720023503039102</v>
       </c>
       <c r="D13">
-        <v>0.7030889017266835</v>
+        <v>0.242492907118557</v>
       </c>
       <c r="E13">
-        <v>-0.1862612705931858</v>
+        <v>-0.1352263645885685</v>
       </c>
       <c r="F13">
-        <v>0.03248630086234521</v>
+        <v>0.1221128504207408</v>
       </c>
       <c r="G13">
-        <v>0.008223024923958308</v>
+        <v>0.004318472892622566</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-1.607573656845754</v>
+        <v>-0.6311101482765262</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -930,25 +930,25 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.01735977721488988</v>
+        <v>-0.006319338162319102</v>
       </c>
       <c r="D14">
-        <v>0.6849878682842294</v>
+        <v>0.2249695744271136</v>
       </c>
       <c r="E14">
-        <v>-0.1831781810905936</v>
+        <v>-0.1312822173884737</v>
       </c>
       <c r="F14">
-        <v>0.03552148348829411</v>
+        <v>0.1334916692113201</v>
       </c>
       <c r="G14">
-        <v>0.008171230661419024</v>
+        <v>0.004185225401526967</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>-1.571783169651455</v>
+        <v>-0.5965443866743696</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -959,25 +959,25 @@
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.01690683217546303</v>
+        <v>-0.005813822354550257</v>
       </c>
       <c r="D15">
-        <v>0.8343468772064961</v>
+        <v>0.372138134668464</v>
       </c>
       <c r="E15">
-        <v>-0.1809355391078904</v>
+        <v>-0.1268040222988226</v>
       </c>
       <c r="F15">
-        <v>0.03787659436807654</v>
+        <v>0.1473749726529866</v>
       </c>
       <c r="G15">
-        <v>0.008060070196882258</v>
+        <v>0.003988752680153612</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-1.363541305603697</v>
+        <v>-0.3836587714230694</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -988,25 +988,25 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.01685350595229278</v>
+        <v>-0.005710236166042058</v>
       </c>
       <c r="D16">
-        <v>0.5685352076513256</v>
+        <v>0.1042322998908787</v>
       </c>
       <c r="E16">
-        <v>-0.1692935190392257</v>
+        <v>-0.09706643009216766</v>
       </c>
       <c r="F16">
-        <v>0.05231093448808986</v>
+        <v>0.2681995859151832</v>
       </c>
       <c r="G16">
-        <v>0.008605256512380833</v>
+        <v>0.005135203984327238</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>-1.622420566146736</v>
+        <v>-0.6380984016945888</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1017,25 +1017,25 @@
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.01556547423306522</v>
+        <v>-0.004412383534047315</v>
       </c>
       <c r="D17">
-        <v>0.6002765260928173</v>
+        <v>0.1355644136337379</v>
       </c>
       <c r="E17">
-        <v>-0.1634458304014108</v>
+        <v>-0.08654292995294469</v>
       </c>
       <c r="F17">
-        <v>0.06112332642005634</v>
+        <v>0.3237905937585115</v>
       </c>
       <c r="G17">
-        <v>0.008240184819246278</v>
+        <v>0.004454895289726097</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>-1.423235124205661</v>
+        <v>-0.4380454457924131</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1046,25 +1046,25 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.01518565722101251</v>
+        <v>-0.00391067166353128</v>
       </c>
       <c r="D18">
-        <v>0.5159474934206303</v>
+        <v>0.04615642852557916</v>
       </c>
       <c r="E18">
-        <v>-0.1570992687524294</v>
+        <v>-0.0699979438283395</v>
       </c>
       <c r="F18">
-        <v>0.07202599615360503</v>
+        <v>0.4251345780700867</v>
       </c>
       <c r="G18">
-        <v>0.008372618013094489</v>
+        <v>0.004887962004770442</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-1.458187945310996</v>
+        <v>-0.4622308877334873</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1075,25 +1075,25 @@
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.01493699704236966</v>
+        <v>-0.003671254696904612</v>
       </c>
       <c r="D19">
-        <v>0.5485610116182038</v>
+        <v>0.07915508055716045</v>
       </c>
       <c r="E19">
-        <v>-0.1608003661844165</v>
+        <v>-0.07537143218158306</v>
       </c>
       <c r="F19">
-        <v>0.06549138964558252</v>
+        <v>0.3903746057297615</v>
       </c>
       <c r="G19">
-        <v>0.008041109876186222</v>
+        <v>0.004259895765843292</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-1.393248603889851</v>
+        <v>-0.398108030040439</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1104,25 +1104,25 @@
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.0146095226809265</v>
+        <v>-0.003361111357991775</v>
       </c>
       <c r="D20">
-        <v>0.5693246036330961</v>
+        <v>0.1006407985108159</v>
       </c>
       <c r="E20">
-        <v>-0.1602598578563123</v>
+        <v>-0.07501731429733768</v>
       </c>
       <c r="F20">
-        <v>0.06641442614929018</v>
+        <v>0.3926113735762038</v>
       </c>
       <c r="G20">
-        <v>0.007892047459744034</v>
+        <v>0.00391853964221522</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>-1.329913344887349</v>
+        <v>-0.3363036780281148</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1133,25 +1133,25 @@
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.01377495543804036</v>
+        <v>-0.002802685074088886</v>
       </c>
       <c r="D21">
-        <v>0.3355025354644074</v>
+        <v>-0.1216753963669042</v>
       </c>
       <c r="E21">
-        <v>-0.115908745682982</v>
+        <v>-0.03262761431041661</v>
       </c>
       <c r="F21">
-        <v>0.1856725907150618</v>
+        <v>0.7103424072657434</v>
       </c>
       <c r="G21">
-        <v>0.0103529760224964</v>
+        <v>0.007529844627339259</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-1.45524167148084</v>
+        <v>-0.4860244559984594</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1162,25 +1162,25 @@
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-0.01331415564344507</v>
+        <v>-0.002150088630157954</v>
       </c>
       <c r="D22">
-        <v>0.653882790936517</v>
+        <v>0.1887133320495538</v>
       </c>
       <c r="E22">
-        <v>-0.1418266652783684</v>
+        <v>-0.04486183605745332</v>
       </c>
       <c r="F22">
-        <v>0.1047654233716014</v>
+        <v>0.6095063501163021</v>
       </c>
       <c r="G22">
-        <v>0.008150263696321543</v>
+        <v>0.004199234955970255</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>-1.076957442711342</v>
+        <v>-0.09079818987098018</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1191,25 +1191,25 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>-0.01207330973154197</v>
+        <v>-0.0006966488418828117</v>
       </c>
       <c r="D23">
-        <v>1.271272995699339</v>
+        <v>0.7972454586302073</v>
       </c>
       <c r="E23">
-        <v>-0.1075284150815871</v>
+        <v>-0.008810067077830575</v>
       </c>
       <c r="F23">
-        <v>0.2197403465638854</v>
+        <v>0.9201385633636305</v>
       </c>
       <c r="G23">
-        <v>0.00979052676708048</v>
+        <v>0.0069349953345481</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>-0.298257269401117</v>
+        <v>0.7066811091854418</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1220,25 +1220,25 @@
         <v>31</v>
       </c>
       <c r="C24">
-        <v>-0.01055034834861525</v>
+        <v>0.0003907261747816355</v>
       </c>
       <c r="D24">
-        <v>1.055388920983375</v>
+        <v>0.5995108158418382</v>
       </c>
       <c r="E24">
-        <v>-0.0891229441486002</v>
+        <v>0.004700529067282214</v>
       </c>
       <c r="F24">
-        <v>0.30952006264001</v>
+        <v>0.9573402176603831</v>
       </c>
       <c r="G24">
-        <v>0.0103412713340683</v>
+        <v>0.0072903652793414</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>-0.316156364336607</v>
+        <v>0.6503052185634508</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1249,83 +1249,83 @@
         <v>32</v>
       </c>
       <c r="C25">
-        <v>-0.009195230265594217</v>
+        <v>0.002058380364099602</v>
       </c>
       <c r="D25">
-        <v>0.2679949932601579</v>
+        <v>-0.2009054496437512</v>
       </c>
       <c r="E25">
-        <v>-0.100870916509646</v>
+        <v>0.04600124527015056</v>
       </c>
       <c r="F25">
-        <v>0.2498005969296761</v>
+        <v>0.6004422327610059</v>
       </c>
       <c r="G25">
-        <v>0.007954340692546061</v>
+        <v>0.003920345747208383</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>-0.9273849412670904</v>
+        <v>0.06668399768919703</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26">
-        <v>-0.008815640383751301</v>
+        <v>0.002565202664336115</v>
       </c>
       <c r="D26">
-        <v>0.3709783683163232</v>
+        <v>0.08904628024905312</v>
       </c>
       <c r="E26">
-        <v>-0.09879207130907347</v>
+        <v>0.0533107104142099</v>
       </c>
       <c r="F26">
-        <v>0.259743180540187</v>
+        <v>0.543784666776705</v>
       </c>
       <c r="G26">
-        <v>0.007788079191376402</v>
+        <v>0.004214223050502674</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>-0.7750548815713458</v>
+        <v>0.422522626612748</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27">
-        <v>-0.008758887456981043</v>
+        <v>0.002567375214168974</v>
       </c>
       <c r="D27">
-        <v>0.5608833686372681</v>
+        <v>-0.1033139482636883</v>
       </c>
       <c r="E27">
-        <v>-0.09445622429520335</v>
+        <v>0.05955810514013513</v>
       </c>
       <c r="F27">
-        <v>0.2813425372378646</v>
+        <v>0.4975404041076982</v>
       </c>
       <c r="G27">
-        <v>0.00809656135172593</v>
+        <v>0.003774028442335724</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>-0.5777720007702676</v>
+        <v>0.2304448295782783</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1336,25 +1336,25 @@
         <v>35</v>
       </c>
       <c r="C28">
-        <v>-0.007929662711638448</v>
+        <v>0.003408869928453985</v>
       </c>
       <c r="D28">
-        <v>0.3306077411900635</v>
+        <v>-0.1418311188137879</v>
       </c>
       <c r="E28">
-        <v>-0.08530625301543525</v>
+        <v>0.06893592064146917</v>
       </c>
       <c r="F28">
-        <v>0.330778723766171</v>
+        <v>0.4322100683000765</v>
       </c>
       <c r="G28">
-        <v>0.00812299489071293</v>
+        <v>0.00432672004596824</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>-0.7002484113229347</v>
+        <v>0.3013219718852301</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1365,25 +1365,25 @@
         <v>36</v>
       </c>
       <c r="C29">
-        <v>-0.007638837290830353</v>
+        <v>0.003728002686061614</v>
       </c>
       <c r="D29">
-        <v>0.5988508890172665</v>
+        <v>0.1252325566467679</v>
       </c>
       <c r="E29">
-        <v>-0.07088682306503555</v>
+        <v>0.05085782555388869</v>
       </c>
       <c r="F29">
-        <v>0.4192643674027062</v>
+        <v>0.5625018732217955</v>
       </c>
       <c r="G29">
-        <v>0.009427491889430982</v>
+        <v>0.006420729438485663</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>-0.3941979587906794</v>
+        <v>0.6098729058347777</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1394,25 +1394,25 @@
         <v>37</v>
       </c>
       <c r="C30">
-        <v>-0.007396692786640792</v>
+        <v>0.003792215358939797</v>
       </c>
       <c r="D30">
-        <v>0.3089742602220937</v>
+        <v>-0.1572302458437641</v>
       </c>
       <c r="E30">
-        <v>-0.07625247221676541</v>
+        <v>0.07006964957945018</v>
       </c>
       <c r="F30">
-        <v>0.384842871292438</v>
+        <v>0.4246592769517883</v>
       </c>
       <c r="G30">
-        <v>0.008482926456500239</v>
+        <v>0.004735028587093226</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>-0.6525958020412093</v>
+        <v>0.3357577508184095</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1423,25 +1423,25 @@
         <v>38</v>
       </c>
       <c r="C31">
-        <v>-0.00665261224429335</v>
+        <v>0.004684187293546046</v>
       </c>
       <c r="D31">
-        <v>0.5095112651646446</v>
+        <v>0.03714461775466987</v>
       </c>
       <c r="E31">
-        <v>-0.06617296879275812</v>
+        <v>0.07579199685680846</v>
       </c>
       <c r="F31">
-        <v>0.4509301359504699</v>
+        <v>0.3877280974092483</v>
       </c>
       <c r="G31">
-        <v>0.008798061017374131</v>
+        <v>0.005404907218396315</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>-0.3553283265934909</v>
+        <v>0.6460889659156559</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1452,25 +1452,25 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>-0.006159698213077757</v>
+        <v>0.00509968942412617</v>
       </c>
       <c r="D32">
-        <v>1.323932344823159</v>
+        <v>0.8547911932729954</v>
       </c>
       <c r="E32">
-        <v>-0.05120454261350543</v>
+        <v>0.05792362796667774</v>
       </c>
       <c r="F32">
-        <v>0.5598376271021979</v>
+        <v>0.5094358371413227</v>
       </c>
       <c r="G32">
-        <v>0.01053681076634849</v>
+        <v>0.007708795246742079</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>0.5231715771230506</v>
+        <v>1.517750818409398</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1481,25 +1481,25 @@
         <v>40</v>
       </c>
       <c r="C33">
-        <v>-0.005799365022935216</v>
+        <v>0.00556920805620979</v>
       </c>
       <c r="D33">
-        <v>0.5680884524038772</v>
+        <v>0.09439790743950188</v>
       </c>
       <c r="E33">
-        <v>-0.05875176854337051</v>
+        <v>0.09443037759334121</v>
       </c>
       <c r="F33">
-        <v>0.5033904440216205</v>
+        <v>0.281474804467794</v>
       </c>
       <c r="G33">
-        <v>0.008642452185960558</v>
+        <v>0.005149499645380876</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>-0.1858290005777009</v>
+        <v>0.8183949547467746</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1510,25 +1510,25 @@
         <v>41</v>
       </c>
       <c r="C34">
-        <v>-0.005083093118448402</v>
+        <v>0.006294723172712778</v>
       </c>
       <c r="D34">
-        <v>-0.1084969510238142</v>
+        <v>-0.5825726298221968</v>
       </c>
       <c r="E34">
-        <v>-0.05263004568515698</v>
+        <v>0.1096368799593862</v>
       </c>
       <c r="F34">
-        <v>0.5489477725638865</v>
+        <v>0.2107785633352086</v>
       </c>
       <c r="G34">
-        <v>0.008459025363370804</v>
+        <v>0.005005210121770344</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>-0.7692990564221065</v>
+        <v>0.2357413826304644</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1539,83 +1539,83 @@
         <v>42</v>
       </c>
       <c r="C35">
-        <v>-0.004579008231001298</v>
+        <v>0.006842713317236714</v>
       </c>
       <c r="D35">
-        <v>-0.1267046665382888</v>
+        <v>-0.6026097310482059</v>
       </c>
       <c r="E35">
-        <v>-0.04883364688320311</v>
+        <v>0.1283703080445441</v>
       </c>
       <c r="F35">
-        <v>0.5781756602491933</v>
+        <v>0.1424002060228351</v>
       </c>
       <c r="G35">
-        <v>0.008214140644072837</v>
+        <v>0.004636432254424376</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>-0.7219757365684576</v>
+        <v>0.2869430001925669</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
       </c>
       <c r="C36">
-        <v>-0.004452453253146496</v>
+        <v>0.006903600013825318</v>
       </c>
       <c r="D36">
-        <v>0.1775036908659094</v>
+        <v>-0.4011238847166058</v>
       </c>
       <c r="E36">
-        <v>-0.0481267291728188</v>
+        <v>0.1451886801737989</v>
       </c>
       <c r="F36">
-        <v>0.5836969519920225</v>
+        <v>0.09670562626229966</v>
       </c>
       <c r="G36">
-        <v>0.008104716156317976</v>
+        <v>0.004126148394213049</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>-0.4013152320431351</v>
+        <v>0.4963441170806856</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
         <v>44</v>
       </c>
       <c r="C37">
-        <v>-0.004417601603736785</v>
+        <v>0.007023572165686553</v>
       </c>
       <c r="D37">
-        <v>0.07059284934848184</v>
+        <v>-0.3006640349188011</v>
       </c>
       <c r="E37">
-        <v>-0.04798120259315904</v>
+        <v>0.1375583075516023</v>
       </c>
       <c r="F37">
-        <v>0.5848365750456381</v>
+        <v>0.1157466768552366</v>
       </c>
       <c r="G37">
-        <v>0.008065722018170688</v>
+        <v>0.00443558855146077</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>-0.5036953591373001</v>
+        <v>0.6124003466204508</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1626,25 +1626,25 @@
         <v>45</v>
       </c>
       <c r="C38">
-        <v>-0.002715821594157815</v>
+        <v>0.008408384067309545</v>
       </c>
       <c r="D38">
-        <v>0.1099911419218178</v>
+        <v>-0.3535174273059888</v>
       </c>
       <c r="E38">
-        <v>-0.02597416066302262</v>
+        <v>0.1282171428041157</v>
       </c>
       <c r="F38">
-        <v>0.7675111841543407</v>
+        <v>0.1428809866123724</v>
       </c>
       <c r="G38">
-        <v>0.009167300955513996</v>
+        <v>0.005704207025809464</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>-0.2430656653186982</v>
+        <v>0.739572501444252</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1655,25 +1655,25 @@
         <v>46</v>
       </c>
       <c r="C39">
-        <v>-0.002536045070533803</v>
+        <v>0.008838882716872321</v>
       </c>
       <c r="D39">
-        <v>-0.1488024905321267</v>
+        <v>-0.6227578150073819</v>
       </c>
       <c r="E39">
-        <v>-0.02671768801103801</v>
+        <v>0.1632620820491144</v>
       </c>
       <c r="F39">
-        <v>0.76105355612361</v>
+        <v>0.06141880956794978</v>
       </c>
       <c r="G39">
-        <v>0.008322069810507675</v>
+        <v>0.004684614685240581</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>-0.4784883497015212</v>
+        <v>0.5262969381860197</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1684,25 +1684,25 @@
         <v>47</v>
       </c>
       <c r="C40">
-        <v>-0.001349032968443713</v>
+        <v>0.009975057152873449</v>
       </c>
       <c r="D40">
-        <v>0.08632556646768084</v>
+        <v>-0.3855115219205343</v>
       </c>
       <c r="E40">
-        <v>-0.01403696615372829</v>
+        <v>0.1835254271625097</v>
       </c>
       <c r="F40">
-        <v>0.8730808239305847</v>
+        <v>0.03516810226268413</v>
       </c>
       <c r="G40">
-        <v>0.008428200223546163</v>
+        <v>0.004686057372801951</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>-0.08904871943000191</v>
+        <v>0.9112459079530142</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1713,25 +1713,25 @@
         <v>48</v>
       </c>
       <c r="C41">
-        <v>-0.0001303905158324539</v>
+        <v>0.01119543270773774</v>
       </c>
       <c r="D41">
-        <v>-0.2298738044803905</v>
+        <v>-0.7017831054624818</v>
       </c>
       <c r="E41">
-        <v>-0.001422587007171103</v>
+        <v>0.2384924890753525</v>
       </c>
       <c r="F41">
-        <v>0.9870837437549744</v>
+        <v>0.005889635939946769</v>
       </c>
       <c r="G41">
-        <v>0.008038870821792242</v>
+        <v>0.003998326779420717</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>-0.2468245715386095</v>
+        <v>0.7536231465434241</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1742,25 +1742,25 @@
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.0002518064258098944</v>
+        <v>0.01187572323690175</v>
       </c>
       <c r="D42">
-        <v>-0.04705603697284817</v>
+        <v>-0.5313859041016757</v>
       </c>
       <c r="E42">
-        <v>0.002818326509322505</v>
+        <v>0.24760147205046</v>
       </c>
       <c r="F42">
-        <v>0.9744144779089743</v>
+        <v>0.004204751735178276</v>
       </c>
       <c r="G42">
-        <v>0.00783613847579742</v>
+        <v>0.004075651836282118</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>-0.0143212016175619</v>
+        <v>1.012458116695552</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1771,25 +1771,25 @@
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.0003062920005727667</v>
+        <v>0.01196949246273337</v>
       </c>
       <c r="D43">
-        <v>0.1223869311252325</v>
+        <v>-0.3635797547981258</v>
       </c>
       <c r="E43">
-        <v>0.003327389223261482</v>
+        <v>0.2257730980904313</v>
       </c>
       <c r="F43">
-        <v>0.9697950860959663</v>
+        <v>0.009242192069643093</v>
       </c>
       <c r="G43">
-        <v>0.00807342785046994</v>
+        <v>0.004529716675316419</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>0.1622048911996921</v>
+        <v>1.192454265357212</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1800,83 +1800,83 @@
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.0008897263080971964</v>
+        <v>0.01228371822028668</v>
       </c>
       <c r="D44">
-        <v>-0.1724774375762246</v>
+        <v>-0.6472271005841197</v>
       </c>
       <c r="E44">
-        <v>0.009163589035299102</v>
+        <v>0.2132254253750449</v>
       </c>
       <c r="F44">
-        <v>0.9169452040855257</v>
+        <v>0.01409738859361635</v>
       </c>
       <c r="G44">
-        <v>0.008515318906570682</v>
+        <v>0.004936453947977981</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>-0.05681301752358908</v>
+        <v>0.9496562680531488</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B45" t="s">
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.002791432253477318</v>
+        <v>0.01450161608081886</v>
       </c>
       <c r="D45">
-        <v>-0.375728480647025</v>
+        <v>-0.7880003851338344</v>
       </c>
       <c r="E45">
-        <v>0.03214974949423369</v>
+        <v>0.2657103079180427</v>
       </c>
       <c r="F45">
-        <v>0.7143994382031913</v>
+        <v>0.002074921793738757</v>
       </c>
       <c r="G45">
-        <v>0.007611202240236833</v>
+        <v>0.004614633333226038</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>-0.0128422876949737</v>
+        <v>1.097209705372618</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.00305389799878535</v>
+        <v>0.014616966626672</v>
       </c>
       <c r="D46">
-        <v>-0.3110121317157714</v>
+        <v>-0.8684590795301367</v>
       </c>
       <c r="E46">
-        <v>0.03222282929323416</v>
+        <v>0.3025547290332419</v>
       </c>
       <c r="F46">
-        <v>0.7137784766665933</v>
+        <v>0.0004218231650990757</v>
       </c>
       <c r="G46">
-        <v>0.00830794470284801</v>
+        <v>0.004038635799612557</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>0.0859946081263242</v>
+        <v>1.031746581937223</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -1887,83 +1887,83 @@
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.003254841082917338</v>
+        <v>0.01485045055720966</v>
       </c>
       <c r="D47">
-        <v>0.01624866807882425</v>
+        <v>-0.4669017266833558</v>
       </c>
       <c r="E47">
-        <v>0.0327184088457845</v>
+        <v>0.2328305004939294</v>
       </c>
       <c r="F47">
-        <v>0.7095724817789599</v>
+        <v>0.007218269858719117</v>
       </c>
       <c r="G47">
-        <v>0.008720338803628595</v>
+        <v>0.005440332350404637</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>0.4393780088580782</v>
+        <v>1.4636568457539</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.005011335772514281</v>
+        <v>0.01667478114029241</v>
       </c>
       <c r="D48">
-        <v>-0.4462377559535272</v>
+        <v>-1.078987675717312</v>
       </c>
       <c r="E48">
-        <v>0.05512020452580395</v>
+        <v>0.3355974856686792</v>
       </c>
       <c r="F48">
-        <v>0.5301761491418182</v>
+        <v>8.362789184353052E-05</v>
       </c>
       <c r="G48">
-        <v>0.007961781540550989</v>
+        <v>0.004105094867047498</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>0.2052358944733293</v>
+        <v>1.088733872520701</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.005204532728969473</v>
+        <v>0.01677043455934271</v>
       </c>
       <c r="D49">
-        <v>-0.6010606585788563</v>
+        <v>-0.9362002054047118</v>
       </c>
       <c r="E49">
-        <v>0.0568700823165629</v>
+        <v>0.3116270990003308</v>
       </c>
       <c r="F49">
-        <v>0.5171806323870285</v>
+        <v>0.0002755397837193795</v>
       </c>
       <c r="G49">
-        <v>0.008013509826736464</v>
+        <v>0.004484917890511626</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>0.07552859618717522</v>
+        <v>1.24395628730984</v>
       </c>
     </row>
   </sheetData>
